--- a/artfynd/A 39170-2026 artfynd.xlsx
+++ b/artfynd/A 39170-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ6"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1205,6 +1205,577 @@
       <c r="AZ6" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/109473326</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>137270980</v>
+      </c>
+      <c r="B7" t="n">
+        <v>93483</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Röbykärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>686116</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6619449</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Två fruktkroppar.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137270980</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>137271358</v>
+      </c>
+      <c r="B8" t="n">
+        <v>93483</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Röbykärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>686162</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6619381</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Fem fruktkroppar.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137271358</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>137271399</v>
+      </c>
+      <c r="B9" t="n">
+        <v>93483</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Röbykärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>686203</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6619380</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>En fruktkropp.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137271399</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>137271433</v>
+      </c>
+      <c r="B10" t="n">
+        <v>93483</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Röbykärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>686247</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6619362</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Två fruktkroppar.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137271433</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>137271303</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57210</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Röbykärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>686176</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6619448</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Spillning, två "högar". Den ena möjligen något äldre än den andra.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137271303</t>
         </is>
       </c>
     </row>
@@ -1215,6 +1786,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39170-2026 artfynd.xlsx
+++ b/artfynd/A 39170-2026 artfynd.xlsx
@@ -1213,7 +1213,7 @@
         <v>137270980</v>
       </c>
       <c r="B7" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>137271358</v>
       </c>
       <c r="B8" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>137271399</v>
       </c>
       <c r="B9" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>137271433</v>
       </c>
       <c r="B10" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>137271303</v>
       </c>
       <c r="B11" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 39170-2026 artfynd.xlsx
+++ b/artfynd/A 39170-2026 artfynd.xlsx
@@ -1213,7 +1213,7 @@
         <v>137270980</v>
       </c>
       <c r="B7" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>137271358</v>
       </c>
       <c r="B8" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>137271399</v>
       </c>
       <c r="B9" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>137271433</v>
       </c>
       <c r="B10" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 39170-2026 artfynd.xlsx
+++ b/artfynd/A 39170-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ11"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1670,52 +1670,57 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>137271303</v>
+        <v>137339315</v>
       </c>
       <c r="B11" t="n">
-        <v>57220</v>
+        <v>93494</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>5966</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Röbykärret, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>686176</v>
+        <v>686151</v>
       </c>
       <c r="R11" t="n">
-        <v>6619448</v>
+        <v>6619333</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1742,14 +1747,19 @@
           <t>2026-10-15</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Spillning, två "högar". Den ena möjligen något äldre än den andra.</t>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1764,16 +1774,248 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Gustav Bringby</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Gustav Bringby</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137339315</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>137339316</v>
+      </c>
+      <c r="B12" t="n">
+        <v>93494</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Röbykärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>686195</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6619357</v>
+      </c>
+      <c r="S12" t="n">
+        <v>9</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Gustav Bringby</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Gustav Bringby</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137339316</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>137271303</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57220</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Röbykärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>686176</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6619448</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Spillning, två "högar". Den ena möjligen något äldre än den andra.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137271303</t>
         </is>
@@ -1791,6 +2033,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39170-2026 artfynd.xlsx
+++ b/artfynd/A 39170-2026 artfynd.xlsx
@@ -1213,7 +1213,7 @@
         <v>137270980</v>
       </c>
       <c r="B7" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>137271358</v>
       </c>
       <c r="B8" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>137271399</v>
       </c>
       <c r="B9" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>137271433</v>
       </c>
       <c r="B10" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>137339315</v>
       </c>
       <c r="B11" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>137339316</v>
       </c>
       <c r="B12" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137271303</v>
       </c>
       <c r="B13" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 39170-2026 artfynd.xlsx
+++ b/artfynd/A 39170-2026 artfynd.xlsx
@@ -1213,7 +1213,7 @@
         <v>137270980</v>
       </c>
       <c r="B7" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>137271358</v>
       </c>
       <c r="B8" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>137271399</v>
       </c>
       <c r="B9" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>137271433</v>
       </c>
       <c r="B10" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>137339315</v>
       </c>
       <c r="B11" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>137339316</v>
       </c>
       <c r="B12" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 39170-2026 artfynd.xlsx
+++ b/artfynd/A 39170-2026 artfynd.xlsx
@@ -1213,7 +1213,7 @@
         <v>137270980</v>
       </c>
       <c r="B7" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
         <v>137271358</v>
       </c>
       <c r="B8" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>137271399</v>
       </c>
       <c r="B9" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>137271433</v>
       </c>
       <c r="B10" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>137339315</v>
       </c>
       <c r="B11" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1794,7 +1794,7 @@
         <v>137339316</v>
       </c>
       <c r="B12" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 39170-2026 artfynd.xlsx
+++ b/artfynd/A 39170-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ13"/>
+  <dimension ref="A1:AZ42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>109473306</v>
+        <v>137427084</v>
       </c>
       <c r="B2" t="n">
-        <v>93197</v>
+        <v>79198</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Norrhall, Upl</t>
+          <t>Ryttartorp, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>686149</v>
+        <v>686224</v>
       </c>
       <c r="R2" t="n">
-        <v>6619054</v>
+        <v>6619468</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-05-11</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-05-11</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,31 +765,27 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>David Falk</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>David Falk, Magnus Nilsson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Stora Obrutna Skogsområden</t>
-        </is>
-      </c>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109473306</t>
+          <t>https://artportalen.se/Sighting/137427084</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>109473323</v>
+        <v>137433308</v>
       </c>
       <c r="B3" t="n">
-        <v>91930</v>
+        <v>91199</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,37 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>889</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vintertagging</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Plicatura pendula</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norrhall, Upl</t>
+          <t>Tjusta, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>686172</v>
+        <v>686143</v>
       </c>
       <c r="R3" t="n">
-        <v>6619077</v>
+        <v>6619086</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -851,12 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-05-11</t>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-05-11</t>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -871,69 +877,69 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>David Falk</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>David Falk, Amelie Lindhagen</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>Stora Obrutna Skogsområden</t>
+          <t>Vallentuna skogsgrupp</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109473323</t>
+          <t>https://artportalen.se/Sighting/137433308</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>109473324</v>
+        <v>137433267</v>
       </c>
       <c r="B4" t="n">
-        <v>91930</v>
+        <v>97015</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Norrhall, Upl</t>
+          <t>Tjusta, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>686147</v>
+        <v>686119</v>
       </c>
       <c r="R4" t="n">
-        <v>6619082</v>
+        <v>6619332</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -957,12 +963,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-05-11</t>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-05-11</t>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -977,69 +993,69 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>David Falk</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>David Falk, Magnus Nilsson</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>Stora Obrutna Skogsområden</t>
+          <t>Vallentuna skogsgrupp</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109473324</t>
+          <t>https://artportalen.se/Sighting/137433267</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>109473325</v>
+        <v>137426478</v>
       </c>
       <c r="B5" t="n">
-        <v>91930</v>
+        <v>92577</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>4217</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Norrhall, Upl</t>
+          <t>Ryttartorp, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>686172</v>
+        <v>686165</v>
       </c>
       <c r="R5" t="n">
-        <v>6619083</v>
+        <v>6619429</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1063,12 +1079,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-05-11</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-05-11</t>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På tallåga.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,31 +1104,27 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>David Falk</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>David Falk, David Falk</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Stora Obrutna Skogsområden</t>
-        </is>
-      </c>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109473325</t>
+          <t>https://artportalen.se/Sighting/137426478</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>109473326</v>
+        <v>109473306</v>
       </c>
       <c r="B6" t="n">
-        <v>91930</v>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1115,21 +1132,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1156,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>686140</v>
+        <v>686149</v>
       </c>
       <c r="R6" t="n">
-        <v>6619081</v>
+        <v>6619054</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1194,7 +1211,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>David Falk, Amelie Lindhagen</t>
+          <t>David Falk, Magnus Nilsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1204,16 +1221,16 @@
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109473326</t>
+          <t>https://artportalen.se/Sighting/109473306</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>137270980</v>
+        <v>137433305</v>
       </c>
       <c r="B7" t="n">
-        <v>93507</v>
+        <v>93481</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,44 +1238,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Röbykärret, Upl</t>
+          <t>Tjusta, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>686116</v>
+        <v>686201</v>
       </c>
       <c r="R7" t="n">
-        <v>6619449</v>
+        <v>6619081</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1282,17 +1292,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Två fruktkroppar.</t>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1301,34 +1316,37 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Vallentuna skogsgrupp</t>
+        </is>
+      </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137270980</t>
+          <t>https://artportalen.se/Sighting/137433305</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>137271358</v>
+        <v>137427414</v>
       </c>
       <c r="B8" t="n">
-        <v>93507</v>
+        <v>93493</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1336,44 +1354,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5966</v>
+        <v>4366</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Röbykärret, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>686162</v>
+        <v>686203</v>
       </c>
       <c r="R8" t="n">
-        <v>6619381</v>
+        <v>6619430</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1397,17 +1408,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Fem fruktkroppar.</t>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1416,34 +1432,33 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Margareta Lysell</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Margareta Lysell</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271358</t>
+          <t>https://artportalen.se/Sighting/137427414</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>137271399</v>
+        <v>109473323</v>
       </c>
       <c r="B9" t="n">
-        <v>93507</v>
+        <v>91930</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1451,44 +1466,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Röbykärret, Upl</t>
+          <t>Norrhall, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>686203</v>
+        <v>686172</v>
       </c>
       <c r="R9" t="n">
-        <v>6619380</v>
+        <v>6619077</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1512,17 +1520,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>En fruktkropp.</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1531,34 +1534,37 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>David Falk</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>David Falk, Amelie Lindhagen</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Stora Obrutna Skogsområden</t>
+        </is>
+      </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271399</t>
+          <t>https://artportalen.se/Sighting/109473323</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>137271433</v>
+        <v>109473324</v>
       </c>
       <c r="B10" t="n">
-        <v>93507</v>
+        <v>91930</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1566,44 +1572,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Röbykärret, Upl</t>
+          <t>Norrhall, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>686247</v>
+        <v>686147</v>
       </c>
       <c r="R10" t="n">
-        <v>6619362</v>
+        <v>6619082</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1627,17 +1626,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Två fruktkroppar.</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1646,34 +1640,37 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>David Falk</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>David Falk, Magnus Nilsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Stora Obrutna Skogsområden</t>
+        </is>
+      </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271433</t>
+          <t>https://artportalen.se/Sighting/109473324</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>137339315</v>
+        <v>109473325</v>
       </c>
       <c r="B11" t="n">
-        <v>93507</v>
+        <v>91930</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1681,46 +1678,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Röbykärret, Upl</t>
+          <t>Norrhall, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>686151</v>
+        <v>686172</v>
       </c>
       <c r="R11" t="n">
-        <v>6619333</v>
+        <v>6619083</v>
       </c>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1744,22 +1732,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>12:15</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>12:15</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1774,27 +1752,31 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Gustav Bringby</t>
+          <t>David Falk</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Gustav Bringby</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>David Falk, David Falk</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Stora Obrutna Skogsområden</t>
+        </is>
+      </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137339315</t>
+          <t>https://artportalen.se/Sighting/109473325</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>137339316</v>
+        <v>109473326</v>
       </c>
       <c r="B12" t="n">
-        <v>93507</v>
+        <v>91930</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1802,46 +1784,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Röbykärret, Upl</t>
+          <t>Norrhall, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>686195</v>
+        <v>686140</v>
       </c>
       <c r="R12" t="n">
-        <v>6619357</v>
+        <v>6619081</v>
       </c>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1865,22 +1838,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:04</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:04</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1895,69 +1858,69 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Gustav Bringby</t>
+          <t>David Falk</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Gustav Bringby</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>David Falk, Amelie Lindhagen</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Stora Obrutna Skogsområden</t>
+        </is>
+      </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137339316</t>
+          <t>https://artportalen.se/Sighting/109473326</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>137271303</v>
+        <v>137427358</v>
       </c>
       <c r="B13" t="n">
-        <v>57221</v>
+        <v>92202</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Röbykärret, Upl</t>
+          <t>Ryttartorp, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>686176</v>
+        <v>686210</v>
       </c>
       <c r="R13" t="n">
-        <v>6619448</v>
+        <v>6619369</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1981,17 +1944,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Spillning, två "högar". Den ena möjligen något äldre än den andra.</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2006,18 +1964,3241 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/137427358</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>137428982</v>
+      </c>
+      <c r="B14" t="n">
+        <v>92202</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Röbykärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>686161</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6619284</v>
+      </c>
+      <c r="S14" t="n">
+        <v>50</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Margareta Lysell</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Margareta Lysell</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137428982</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>137430602</v>
+      </c>
+      <c r="B15" t="n">
+        <v>93507</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Röbykärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>686236</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6619103</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Kalle Skarin</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Kalle Skarin</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137430602</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>137430718</v>
+      </c>
+      <c r="B16" t="n">
+        <v>93507</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Röbykärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>686172</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6619072</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Kalle Skarin</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Kalle Skarin</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137430718</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>137433304</v>
+      </c>
+      <c r="B17" t="n">
+        <v>93507</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Tjusta, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>686238</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6619102</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Vallentuna skogsgrupp</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433304</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>137433306</v>
+      </c>
+      <c r="B18" t="n">
+        <v>93507</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Tjusta, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>686164</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6619072</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Vallentuna skogsgrupp</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433306</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>137270980</v>
+      </c>
+      <c r="B19" t="n">
+        <v>93519</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Röbykärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>686116</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6619449</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Två fruktkroppar.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137270980</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>137271358</v>
+      </c>
+      <c r="B20" t="n">
+        <v>93519</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Röbykärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>686162</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6619381</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Fem fruktkroppar.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137271358</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>137271399</v>
+      </c>
+      <c r="B21" t="n">
+        <v>93519</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Röbykärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>686203</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6619380</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>En fruktkropp.</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137271399</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>137271433</v>
+      </c>
+      <c r="B22" t="n">
+        <v>93519</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Röbykärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>686247</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6619362</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Två fruktkroppar.</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137271433</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>137339315</v>
+      </c>
+      <c r="B23" t="n">
+        <v>93519</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Röbykärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>686151</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6619333</v>
+      </c>
+      <c r="S23" t="n">
+        <v>9</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Gustav Bringby</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Gustav Bringby</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137339315</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>137339316</v>
+      </c>
+      <c r="B24" t="n">
+        <v>93519</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Röbykärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>686195</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6619357</v>
+      </c>
+      <c r="S24" t="n">
+        <v>9</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Gustav Bringby</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Gustav Bringby</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137339316</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>137425160</v>
+      </c>
+      <c r="B25" t="n">
+        <v>93519</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Ryttartorp, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>686112</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6619358</v>
+      </c>
+      <c r="S25" t="n">
+        <v>9</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137425160</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>137427837</v>
+      </c>
+      <c r="B26" t="n">
+        <v>93519</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Röbykärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>686161</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6619284</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Margareta Lysell</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Margareta Lysell</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137427837</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>137433268</v>
+      </c>
+      <c r="B27" t="n">
+        <v>93519</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Tjusta, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>686116</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6619345</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Vallentuna skogsgrupp</t>
+        </is>
+      </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433268</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>137433270</v>
+      </c>
+      <c r="B28" t="n">
+        <v>93519</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Tjusta, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>686254</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6619373</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Vallentuna skogsgrupp</t>
+        </is>
+      </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433270</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>137433303</v>
+      </c>
+      <c r="B29" t="n">
+        <v>93519</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Tjusta, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>686260</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6619095</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Vallentuna skogsgrupp</t>
+        </is>
+      </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433303</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>137426354</v>
+      </c>
+      <c r="B30" t="n">
+        <v>80151</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Ryttartorp, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>686152</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6619427</v>
+      </c>
+      <c r="S30" t="n">
+        <v>6</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137426354</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>137426650</v>
+      </c>
+      <c r="B31" t="n">
+        <v>80151</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Ryttartorp, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>686175</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6619445</v>
+      </c>
+      <c r="S31" t="n">
+        <v>9</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137426650</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>137426764</v>
+      </c>
+      <c r="B32" t="n">
+        <v>80151</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Ryttartorp, Upl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>686156</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6619439</v>
+      </c>
+      <c r="S32" t="n">
+        <v>8</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137426764</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>137425381</v>
+      </c>
+      <c r="B33" t="n">
+        <v>58032</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Ryttartorp, Upl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>686145</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6619351</v>
+      </c>
+      <c r="S33" t="n">
+        <v>7</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137425381</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>137433307</v>
+      </c>
+      <c r="B34" t="n">
+        <v>58032</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Tjusta, Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>686149</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6619071</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Vallentuna skogsgrupp</t>
+        </is>
+      </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433307</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>137426689</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57981</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100067</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Havsörn</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Haliaeetus albicilla</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Ryttartorp, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>686156</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6619439</v>
+      </c>
+      <c r="S35" t="n">
+        <v>20</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137426689</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>137271303</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57221</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Röbykärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>686176</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6619448</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Spillning, två "högar". Den ena möjligen något äldre än den andra.</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Mattias Bergström</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/137271303</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>137426373</v>
+      </c>
+      <c r="B37" t="n">
+        <v>8470</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Röbykärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>686189</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6619372</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Birgitta Tulin</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Birgitta Tulin</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137426373</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>137426543</v>
+      </c>
+      <c r="B38" t="n">
+        <v>8470</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Ryttartorp, Upl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>686165</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6619429</v>
+      </c>
+      <c r="S38" t="n">
+        <v>9</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Ronny Fors</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137426543</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>137429955</v>
+      </c>
+      <c r="B39" t="n">
+        <v>98292</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Röbykärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>686161</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6619284</v>
+      </c>
+      <c r="S39" t="n">
+        <v>50</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Margareta Lysell</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Margareta Lysell</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137429955</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>137430313</v>
+      </c>
+      <c r="B40" t="n">
+        <v>101646</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Röbykärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>686161</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6619284</v>
+      </c>
+      <c r="S40" t="n">
+        <v>50</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:55</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Margareta Lysell</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Margareta Lysell</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137430313</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>137423557</v>
+      </c>
+      <c r="B41" t="n">
+        <v>92572</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6040162</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Tallkötticka</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Leptoporus erubescens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Röbykärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>686087</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6619346</v>
+      </c>
+      <c r="S41" t="n">
+        <v>50</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Vanja Ekerhult</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Vanja Ekerhult</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137423557</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>137433269</v>
+      </c>
+      <c r="B42" t="n">
+        <v>92572</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6040162</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Tallkötticka</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Leptoporus erubescens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Tjusta, Upl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>686089</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6619357</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr">
+        <is>
+          <t>Vallentuna skogsgrupp</t>
+        </is>
+      </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137433269</t>
         </is>
       </c>
     </row>
@@ -2035,6 +5216,35 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39170-2026 artfynd.xlsx
+++ b/artfynd/A 39170-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ42"/>
+  <dimension ref="A1:AZ44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>137427084</v>
       </c>
       <c r="B2" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Ronny Fors, Mia Agvald Jägborn</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -785,7 +785,7 @@
         <v>137433308</v>
       </c>
       <c r="B3" t="n">
-        <v>91199</v>
+        <v>91200</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>137433267</v>
       </c>
       <c r="B4" t="n">
-        <v>97015</v>
+        <v>97016</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>137426478</v>
       </c>
       <c r="B5" t="n">
-        <v>92577</v>
+        <v>92578</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Ronny Fors, Mia Agvald Jägborn</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1230,7 +1230,7 @@
         <v>137433305</v>
       </c>
       <c r="B7" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>137427414</v>
       </c>
       <c r="B8" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Margareta Lysell</t>
+          <t>Margareta Lysell, Mia Agvald Jägborn</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1882,7 +1882,7 @@
         <v>137427358</v>
       </c>
       <c r="B13" t="n">
-        <v>92202</v>
+        <v>92203</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Ronny Fors, Mia Agvald Jägborn</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1984,7 +1984,7 @@
         <v>137428982</v>
       </c>
       <c r="B14" t="n">
-        <v>92202</v>
+        <v>92203</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         <v>137430602</v>
       </c>
       <c r="B15" t="n">
-        <v>93507</v>
+        <v>93508</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>137430718</v>
       </c>
       <c r="B16" t="n">
-        <v>93507</v>
+        <v>93508</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>137433304</v>
       </c>
       <c r="B17" t="n">
-        <v>93507</v>
+        <v>93508</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2416,7 +2416,7 @@
         <v>137433306</v>
       </c>
       <c r="B18" t="n">
-        <v>93507</v>
+        <v>93508</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         <v>137270980</v>
       </c>
       <c r="B19" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>137271358</v>
       </c>
       <c r="B20" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>137271399</v>
       </c>
       <c r="B21" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>137271433</v>
       </c>
       <c r="B22" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>137339315</v>
       </c>
       <c r="B23" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
         <v>137339316</v>
       </c>
       <c r="B24" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         <v>137425160</v>
       </c>
       <c r="B25" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3321,7 +3321,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Ronny Fors, Mia Agvald Jägborn</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3336,7 +3336,7 @@
         <v>137427837</v>
       </c>
       <c r="B26" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>137433268</v>
       </c>
       <c r="B27" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3564,7 +3564,7 @@
         <v>137433270</v>
       </c>
       <c r="B28" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>137433303</v>
       </c>
       <c r="B29" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3793,10 +3793,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>137426354</v>
+        <v>137442533</v>
       </c>
       <c r="B30" t="n">
-        <v>80151</v>
+        <v>93520</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3804,37 +3804,48 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Ryttartorp, Upl</t>
+          <t>Röbykärret, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>686152</v>
+        <v>686018</v>
       </c>
       <c r="R30" t="n">
-        <v>6619427</v>
+        <v>6619318</v>
       </c>
       <c r="S30" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3861,44 +3872,55 @@
           <t>2026-10-24</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2026-10-24</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Gustav Bringby</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Gustav Bringby</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137426354</t>
+          <t>https://artportalen.se/Sighting/137442533</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>137426650</v>
+        <v>137426354</v>
       </c>
       <c r="B31" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3930,13 +3952,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>686175</v>
+        <v>686152</v>
       </c>
       <c r="R31" t="n">
-        <v>6619445</v>
+        <v>6619427</v>
       </c>
       <c r="S31" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3985,22 +4007,22 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Ronny Fors, Mia Agvald Jägborn</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137426650</t>
+          <t>https://artportalen.se/Sighting/137426354</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>137426764</v>
+        <v>137426650</v>
       </c>
       <c r="B32" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4032,13 +4054,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>686156</v>
+        <v>686175</v>
       </c>
       <c r="R32" t="n">
-        <v>6619439</v>
+        <v>6619445</v>
       </c>
       <c r="S32" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4087,61 +4109,60 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Ronny Fors, Mia Agvald Jägborn</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137426764</t>
+          <t>https://artportalen.se/Sighting/137426650</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>137425381</v>
+        <v>137426764</v>
       </c>
       <c r="B33" t="n">
-        <v>58032</v>
+        <v>80152</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Ryttartorp, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>686145</v>
+        <v>686156</v>
       </c>
       <c r="R33" t="n">
-        <v>6619351</v>
+        <v>6619439</v>
       </c>
       <c r="S33" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4190,19 +4211,19 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Ronny Fors, Mia Agvald Jägborn</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137425381</t>
+          <t>https://artportalen.se/Sighting/137426764</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>137433307</v>
+        <v>137425381</v>
       </c>
       <c r="B34" t="n">
         <v>58032</v>
@@ -4231,23 +4252,20 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Tjusta, Upl</t>
+          <t>Ryttartorp, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>686149</v>
+        <v>686145</v>
       </c>
       <c r="R34" t="n">
-        <v>6619071</v>
+        <v>6619351</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4274,19 +4292,9 @@
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>15:11</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>15:11</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4301,31 +4309,27 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Liam Sebestyén</t>
-        </is>
-      </c>
-      <c r="AY34" t="inlineStr">
-        <is>
-          <t>Vallentuna skogsgrupp</t>
-        </is>
-      </c>
+          <t>Ronny Fors, Mia Agvald Jägborn</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137433307</t>
+          <t>https://artportalen.se/Sighting/137425381</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>137426689</v>
+        <v>137433307</v>
       </c>
       <c r="B35" t="n">
-        <v>57981</v>
+        <v>58032</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4333,16 +4337,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100067</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4352,20 +4356,22 @@
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Ryttartorp, Upl</t>
+          <t>Tjusta, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>686156</v>
+        <v>686149</v>
       </c>
       <c r="R35" t="n">
-        <v>6619439</v>
+        <v>6619071</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4392,9 +4398,19 @@
           <t>2026-10-24</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:11</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:11</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4409,27 +4425,31 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Liam Sebestyén</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
+          <t>Liam Sebestyén</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Vallentuna skogsgrupp</t>
+        </is>
+      </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137426689</t>
+          <t>https://artportalen.se/Sighting/137433307</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>137271303</v>
+        <v>137426689</v>
       </c>
       <c r="B36" t="n">
-        <v>57221</v>
+        <v>57981</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4437,41 +4457,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100138</v>
+        <v>100067</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Röbykärret, Upl</t>
+          <t>Ryttartorp, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>686176</v>
+        <v>686156</v>
       </c>
       <c r="R36" t="n">
-        <v>6619448</v>
+        <v>6619439</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4495,17 +4513,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Spillning, två "högar". Den ena möjligen något äldre än den andra.</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4520,27 +4533,27 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Mattias Bergström</t>
+          <t>Ronny Fors, Mia Agvald Jägborn</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137271303</t>
+          <t>https://artportalen.se/Sighting/137426689</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>137426373</v>
+        <v>137271303</v>
       </c>
       <c r="B37" t="n">
-        <v>8470</v>
+        <v>57221</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4548,34 +4561,38 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Röbykärret, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>686189</v>
+        <v>686176</v>
       </c>
       <c r="R37" t="n">
-        <v>6619372</v>
+        <v>6619448</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4602,22 +4619,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>12:41</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>12:41</t>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Spillning, två "högar". Den ena möjligen något äldre än den andra.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4632,24 +4644,24 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Birgitta Tulin</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Birgitta Tulin</t>
+          <t>Mattias Bergström</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137426373</t>
+          <t>https://artportalen.se/Sighting/137271303</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>137426543</v>
+        <v>137426373</v>
       </c>
       <c r="B38" t="n">
         <v>8470</v>
@@ -4678,20 +4690,19 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Ryttartorp, Upl</t>
+          <t>Röbykärret, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>686165</v>
+        <v>686189</v>
       </c>
       <c r="R38" t="n">
-        <v>6619429</v>
+        <v>6619372</v>
       </c>
       <c r="S38" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4718,9 +4729,19 @@
           <t>2026-10-24</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4735,27 +4756,27 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Birgitta Tulin</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Ronny Fors</t>
+          <t>Birgitta Tulin</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137426543</t>
+          <t>https://artportalen.se/Sighting/137426373</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>137429955</v>
+        <v>137426543</v>
       </c>
       <c r="B39" t="n">
-        <v>98292</v>
+        <v>8470</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4763,37 +4784,38 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221945</v>
+        <v>106545</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Röbykärret, Upl</t>
+          <t>Ryttartorp, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>686161</v>
+        <v>686165</v>
       </c>
       <c r="R39" t="n">
-        <v>6619284</v>
+        <v>6619429</v>
       </c>
       <c r="S39" t="n">
-        <v>50</v>
+        <v>9</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4820,19 +4842,9 @@
           <t>2026-10-24</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>14:40</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-10-24</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>14:40</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4847,27 +4859,27 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Margareta Lysell</t>
+          <t>Ronny Fors</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Margareta Lysell</t>
+          <t>Ronny Fors, Mia Agvald Jägborn</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137429955</t>
+          <t>https://artportalen.se/Sighting/137426543</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>137430313</v>
+        <v>137442534</v>
       </c>
       <c r="B40" t="n">
-        <v>101646</v>
+        <v>8470</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4875,37 +4887,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>222498</v>
+        <v>106545</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Röbykärret, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>686161</v>
+        <v>686167</v>
       </c>
       <c r="R40" t="n">
-        <v>6619284</v>
+        <v>6619436</v>
       </c>
       <c r="S40" t="n">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4934,7 +4951,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4944,7 +4961,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>12:48</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Gnagspår</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4953,55 +4975,56 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Margareta Lysell</t>
+          <t>Gustav Bringby</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Margareta Lysell</t>
+          <t>Gustav Bringby</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137430313</t>
+          <t>https://artportalen.se/Sighting/137442534</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>137423557</v>
+        <v>137429955</v>
       </c>
       <c r="B41" t="n">
-        <v>92572</v>
+        <v>98293</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6040162</v>
+        <v>221945</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tallkötticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5011,10 +5034,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>686087</v>
+        <v>686161</v>
       </c>
       <c r="R41" t="n">
-        <v>6619346</v>
+        <v>6619284</v>
       </c>
       <c r="S41" t="n">
         <v>50</v>
@@ -5046,7 +5069,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5056,7 +5079,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5071,65 +5094,65 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Vanja Ekerhult</t>
+          <t>Margareta Lysell</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Vanja Ekerhult</t>
+          <t>Margareta Lysell</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137423557</t>
+          <t>https://artportalen.se/Sighting/137429955</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>137433269</v>
+        <v>137430313</v>
       </c>
       <c r="B42" t="n">
-        <v>92572</v>
+        <v>101647</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6040162</v>
+        <v>222498</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tallkötticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Tjusta, Upl</t>
+          <t>Röbykärret, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>686089</v>
+        <v>686161</v>
       </c>
       <c r="R42" t="n">
-        <v>6619357</v>
+        <v>6619284</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5158,7 +5181,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5168,7 +5191,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5183,20 +5206,244 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
+          <t>Margareta Lysell</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Margareta Lysell</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137430313</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>137423557</v>
+      </c>
+      <c r="B43" t="n">
+        <v>92573</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6040162</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Tallkötticka</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Leptoporus erubescens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Röbykärret, Upl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>686087</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6619346</v>
+      </c>
+      <c r="S43" t="n">
+        <v>50</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Vanja Ekerhult</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Vanja Ekerhult</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137423557</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>137433269</v>
+      </c>
+      <c r="B44" t="n">
+        <v>92573</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6040162</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tallkötticka</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Leptoporus erubescens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Tjusta, Upl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>686089</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6619357</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Vallentuna</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Kårsta</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
           <t>Liam Sebestyén</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
+      <c r="AX44" t="inlineStr">
         <is>
           <t>Liam Sebestyén</t>
         </is>
       </c>
-      <c r="AY42" t="inlineStr">
+      <c r="AY44" t="inlineStr">
         <is>
           <t>Vallentuna skogsgrupp</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
+      <c r="AZ44" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137433269</t>
         </is>
@@ -5245,6 +5492,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39170-2026 artfynd.xlsx
+++ b/artfynd/A 39170-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137427084</v>
       </c>
       <c r="B2" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137433308</v>
       </c>
       <c r="B3" t="n">
-        <v>91200</v>
+        <v>91203</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>137433267</v>
       </c>
       <c r="B4" t="n">
-        <v>97016</v>
+        <v>97019</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>137426478</v>
       </c>
       <c r="B5" t="n">
-        <v>92578</v>
+        <v>92581</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>137433305</v>
       </c>
       <c r="B7" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>137427414</v>
       </c>
       <c r="B8" t="n">
-        <v>93494</v>
+        <v>93497</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>137427358</v>
       </c>
       <c r="B13" t="n">
-        <v>92203</v>
+        <v>92206</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>137428982</v>
       </c>
       <c r="B14" t="n">
-        <v>92203</v>
+        <v>92206</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         <v>137430602</v>
       </c>
       <c r="B15" t="n">
-        <v>93508</v>
+        <v>93511</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>137430718</v>
       </c>
       <c r="B16" t="n">
-        <v>93508</v>
+        <v>93511</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>137433304</v>
       </c>
       <c r="B17" t="n">
-        <v>93508</v>
+        <v>93511</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2416,7 +2416,7 @@
         <v>137433306</v>
       </c>
       <c r="B18" t="n">
-        <v>93508</v>
+        <v>93511</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         <v>137270980</v>
       </c>
       <c r="B19" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>137271358</v>
       </c>
       <c r="B20" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>137271399</v>
       </c>
       <c r="B21" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>137271433</v>
       </c>
       <c r="B22" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>137339315</v>
       </c>
       <c r="B23" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
         <v>137339316</v>
       </c>
       <c r="B24" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         <v>137425160</v>
       </c>
       <c r="B25" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>137427837</v>
       </c>
       <c r="B26" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>137433268</v>
       </c>
       <c r="B27" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3564,7 +3564,7 @@
         <v>137433270</v>
       </c>
       <c r="B28" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>137433303</v>
       </c>
       <c r="B29" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3796,7 +3796,7 @@
         <v>137442533</v>
       </c>
       <c r="B30" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
         <v>137426354</v>
       </c>
       <c r="B31" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>137426650</v>
       </c>
       <c r="B32" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>137426764</v>
       </c>
       <c r="B33" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5002,7 +5002,7 @@
         <v>137429955</v>
       </c>
       <c r="B41" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>137430313</v>
       </c>
       <c r="B42" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>137423557</v>
       </c>
       <c r="B43" t="n">
-        <v>92573</v>
+        <v>92576</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>137433269</v>
       </c>
       <c r="B44" t="n">
-        <v>92573</v>
+        <v>92576</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 39170-2026 artfynd.xlsx
+++ b/artfynd/A 39170-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137427084</v>
       </c>
       <c r="B2" t="n">
-        <v>79201</v>
+        <v>79205</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137433308</v>
       </c>
       <c r="B3" t="n">
-        <v>91203</v>
+        <v>91207</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>137433267</v>
       </c>
       <c r="B4" t="n">
-        <v>97019</v>
+        <v>97023</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>137426478</v>
       </c>
       <c r="B5" t="n">
-        <v>92581</v>
+        <v>92585</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
         <v>137433305</v>
       </c>
       <c r="B7" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>137427414</v>
       </c>
       <c r="B8" t="n">
-        <v>93497</v>
+        <v>93501</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>137427358</v>
       </c>
       <c r="B13" t="n">
-        <v>92206</v>
+        <v>92210</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>137428982</v>
       </c>
       <c r="B14" t="n">
-        <v>92206</v>
+        <v>92210</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         <v>137430602</v>
       </c>
       <c r="B15" t="n">
-        <v>93511</v>
+        <v>93515</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>137430718</v>
       </c>
       <c r="B16" t="n">
-        <v>93511</v>
+        <v>93515</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>137433304</v>
       </c>
       <c r="B17" t="n">
-        <v>93511</v>
+        <v>93515</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2416,7 +2416,7 @@
         <v>137433306</v>
       </c>
       <c r="B18" t="n">
-        <v>93511</v>
+        <v>93515</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         <v>137270980</v>
       </c>
       <c r="B19" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>137271358</v>
       </c>
       <c r="B20" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>137271399</v>
       </c>
       <c r="B21" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>137271433</v>
       </c>
       <c r="B22" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>137339315</v>
       </c>
       <c r="B23" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
         <v>137339316</v>
       </c>
       <c r="B24" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         <v>137425160</v>
       </c>
       <c r="B25" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>137427837</v>
       </c>
       <c r="B26" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3448,7 +3448,7 @@
         <v>137433268</v>
       </c>
       <c r="B27" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3564,7 +3564,7 @@
         <v>137433270</v>
       </c>
       <c r="B28" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>137433303</v>
       </c>
       <c r="B29" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3796,7 +3796,7 @@
         <v>137442533</v>
       </c>
       <c r="B30" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3920,7 +3920,7 @@
         <v>137426354</v>
       </c>
       <c r="B31" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4022,7 +4022,7 @@
         <v>137426650</v>
       </c>
       <c r="B32" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4124,7 +4124,7 @@
         <v>137426764</v>
       </c>
       <c r="B33" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4226,7 +4226,7 @@
         <v>137425381</v>
       </c>
       <c r="B34" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4329,7 +4329,7 @@
         <v>137433307</v>
       </c>
       <c r="B35" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4449,7 +4449,7 @@
         <v>137426689</v>
       </c>
       <c r="B36" t="n">
-        <v>57981</v>
+        <v>57984</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
         <v>137271303</v>
       </c>
       <c r="B37" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5002,7 +5002,7 @@
         <v>137429955</v>
       </c>
       <c r="B41" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>137430313</v>
       </c>
       <c r="B42" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>137423557</v>
       </c>
       <c r="B43" t="n">
-        <v>92576</v>
+        <v>92580</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>137433269</v>
       </c>
       <c r="B44" t="n">
-        <v>92576</v>
+        <v>92580</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
